--- a/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:30:54+00:00</t>
+    <t>2024-02-12T16:35:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot</t>
+    <t>1.0.1-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T16:35:53+00:00</t>
+    <t>2024-02-15T10:34:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:34:46+00:00</t>
+    <t>2024-02-15T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T10:52:57+00:00</t>
+    <t>2024-02-15T11:14:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/nriss-patch-1/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-15T11:14:23+00:00</t>
+    <t>2024-02-16T11:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
